--- a/tools/excel/intuitem/vendor-due-diligence.xlsx
+++ b/tools/excel/intuitem/vendor-due-diligence.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abder/mydev/intuitem/staging/ciso-assistant-community/tools/excel/intuitem/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JulianDoloir\Desktop\Repos\intuitem\ciso-assistant-community\tools\excel\intuitem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70CC37E0-2542-3243-890D-63DC29644FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2968288-3CFF-437C-9EB2-9E145729FA9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="840" windowWidth="34240" windowHeight="21340" activeTab="2" xr2:uid="{C1B9C957-850F-8443-8E06-CB4E729FFF6E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{C1B9C957-850F-8443-8E06-CB4E729FFF6E}"/>
   </bookViews>
   <sheets>
     <sheet name="library_meta" sheetId="4" r:id="rId1"/>
@@ -20,7 +20,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">objectives_content!$A$1:$F$56</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="192">
   <si>
     <t>name</t>
   </si>
@@ -70,9 +70,6 @@
     <t>version</t>
   </si>
   <si>
-    <t>publication_date</t>
-  </si>
-  <si>
     <t>locale</t>
   </si>
   <si>
@@ -436,9 +433,6 @@
     <t>urn:intuitem:risk:framework:vendor-due-diligence</t>
   </si>
   <si>
-    <t>Vendor Due Diligence - simple</t>
-  </si>
-  <si>
     <t>Sécurité du développement</t>
   </si>
   <si>
@@ -617,15 +611,28 @@
   </si>
   <si>
     <t>Penetration tests (pentests) are conducted regularly by an independent entity.</t>
+  </si>
+  <si>
+    <t>Vendor Due Diligence (VDD) - simple</t>
+  </si>
+  <si>
+    <t>Framework simplifié pour l'évaluation rapide de la cybersécurité des fournisseurs</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -679,14 +686,15 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="22" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -706,7 +714,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1022,15 +1030,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42A14827-EDC4-A84F-B393-2E57779FA06F}">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="54.1640625" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.83203125" style="1"/>
+    <col min="2" max="2" width="60.3984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -1038,84 +1046,92 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B3" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="2">
-        <v>45960</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B4" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>14</v>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -1126,60 +1142,76 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{673D17F9-05BA-F543-9567-B2001588087D}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="51" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.83203125" style="1"/>
+    <col min="2" max="2" width="61.296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="B2" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B5" s="5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>128</v>
+      <c r="B6" s="5" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -1191,18 +1223,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C66D1A5-D362-274A-84D5-DA2AC26B176B}">
   <dimension ref="A1:G56"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="8.83203125" style="1"/>
-    <col min="3" max="3" width="7.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="8.796875" style="1"/>
+    <col min="3" max="3" width="7.796875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="28.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="105.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="105.296875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="29" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="76.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.83203125" style="1"/>
+    <col min="7" max="7" width="76.296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1219,923 +1251,923 @@
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="D2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="1">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1">
+        <v>2</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1">
+        <v>2</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="1">
+        <v>2</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1">
+        <v>2</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1">
+        <v>2</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="1">
+        <v>2</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="1">
+        <v>2</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="1">
+        <v>2</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="1">
+        <v>2</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="1">
+        <v>2</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="2">
+        <v>1</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="1">
+        <v>2</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="1">
+        <v>2</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="1">
+        <v>2</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="1">
+        <v>2</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="2">
+        <v>1</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="1">
+        <v>2</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" s="1">
+        <v>2</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" s="1">
+        <v>2</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" s="1">
+        <v>2</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="1">
+        <v>2</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" s="1">
+        <v>2</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="1">
+        <v>2</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="2">
+        <v>1</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" s="1">
+        <v>2</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" s="1">
+        <v>2</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="3">
+      <c r="G32" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33" s="1">
+        <v>2</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="2">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="1">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="1">
-        <v>2</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="1">
-        <v>2</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="1">
-        <v>2</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="1">
-        <v>2</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="1">
-        <v>2</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="1">
-        <v>2</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1">
-        <v>2</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="3">
+      <c r="C34" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35" s="1">
+        <v>2</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B36" s="1">
+        <v>2</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B37" s="3">
         <v>1</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="1">
-        <v>2</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="1">
-        <v>2</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="1">
-        <v>2</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="1">
-        <v>2</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="1">
-        <v>2</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="3">
+      <c r="C37" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B38" s="1">
+        <v>2</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B39" s="1">
+        <v>2</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B40" s="1">
+        <v>2</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B41" s="1">
+        <v>2</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B42" s="1">
+        <v>2</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B43" s="1">
+        <v>2</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="2">
         <v>1</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="1">
-        <v>2</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="1">
-        <v>2</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="1">
-        <v>2</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B21" s="1">
-        <v>2</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="3">
+      <c r="C44" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B45" s="1">
+        <v>2</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B46" s="1">
+        <v>2</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B47" s="1">
+        <v>2</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="2">
         <v>1</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B23" s="1">
-        <v>2</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B24" s="1">
-        <v>2</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B25" s="1">
-        <v>2</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B26" s="1">
-        <v>2</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B27" s="1">
-        <v>2</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B28" s="1">
-        <v>2</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B29" s="1">
-        <v>2</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="3">
-        <v>1</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B31" s="1">
-        <v>2</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B32" s="1">
-        <v>2</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B33" s="1">
-        <v>2</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="3">
-        <v>1</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B35" s="1">
-        <v>2</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B36" s="1">
-        <v>2</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B37" s="4">
-        <v>1</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B38" s="1">
-        <v>2</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B39" s="1">
-        <v>2</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A40" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B40" s="1">
-        <v>2</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A41" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B41" s="1">
-        <v>2</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A42" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B42" s="1">
-        <v>2</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A43" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B43" s="1">
-        <v>2</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="3">
-        <v>1</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A45" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B45" s="1">
-        <v>2</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A46" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B46" s="1">
-        <v>2</v>
-      </c>
-      <c r="C46" s="1" t="s">
+      <c r="C48" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B49" s="1">
+        <v>2</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E46" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A47" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B47" s="1">
-        <v>2</v>
-      </c>
-      <c r="C47" s="1" t="s">
+      <c r="E49" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B50" s="1">
+        <v>2</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="3">
-        <v>1</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A49" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B49" s="1">
-        <v>2</v>
-      </c>
-      <c r="C49" s="1" t="s">
+      <c r="E50" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B51" s="1">
+        <v>2</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="E49" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A50" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B50" s="1">
-        <v>2</v>
-      </c>
-      <c r="C50" s="1" t="s">
+      <c r="E51" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B52" s="1">
+        <v>2</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="E50" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A51" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B51" s="1">
-        <v>2</v>
-      </c>
-      <c r="C51" s="1" t="s">
+      <c r="E52" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B53" s="1">
+        <v>2</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="E51" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A52" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B52" s="1">
-        <v>2</v>
-      </c>
-      <c r="C52" s="1" t="s">
+      <c r="E53" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B54" s="1">
+        <v>2</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A53" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B53" s="1">
-        <v>2</v>
-      </c>
-      <c r="C53" s="1" t="s">
+      <c r="E54" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B55" s="1">
+        <v>2</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E53" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A54" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B54" s="1">
-        <v>2</v>
-      </c>
-      <c r="C54" s="1" t="s">
+      <c r="E55" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B56" s="1">
+        <v>2</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="E54" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A55" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B55" s="1">
-        <v>2</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G55" s="1" t="s">
+      <c r="E56" s="1" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A56" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B56" s="1">
-        <v>2</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E56" s="1" t="s">
+      <c r="G56" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="G56" s="1" t="s">
-        <v>124</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
